--- a/artfynd/A 48652-2025 artfynd.xlsx
+++ b/artfynd/A 48652-2025 artfynd.xlsx
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67581057</v>
+        <v>67581059</v>
       </c>
       <c r="B2" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Iliden, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576938.1918781688</v>
+        <v>577011</v>
       </c>
       <c r="R2" t="n">
-        <v>7208234.836910782</v>
+        <v>7208476</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,27 +746,23 @@
           <t>2017-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Jag har fått 31 av mina sotlavkollekter kontrollbestämda av Anders Nordin och 18 av dem visade sig vara Liten sotlav Acolium karelicum. Därefter tappade jag bort kollekterna. Allt som kan sägas nu är att arton trettioendelar av mina sotlavkollekter är liten sotlav, det går inte att säga vilka som är det. Därför har jag bockat för "osäker artbestämning".</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -814,15 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67581058</v>
+        <v>67581057</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,21 +819,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -854,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576938.1918781688</v>
+        <v>576938</v>
       </c>
       <c r="R3" t="n">
-        <v>7208234.836910782</v>
+        <v>7208235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,19 +876,9 @@
           <t>2017-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -953,48 +932,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67581059</v>
+        <v>67581058</v>
       </c>
       <c r="B4" t="n">
-        <v>78693</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Iliden, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577011</v>
+        <v>576938</v>
       </c>
       <c r="R4" t="n">
-        <v>7208476</v>
+        <v>7208235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,18 +1005,12 @@
           <t>2017-08-19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Jag har fått 31 av mina sotlavkollekter kontrollbestämda av Anders Nordin och 18 av dem visade sig vara Liten sotlav Acolium karelicum. Därefter tappade jag bort kollekterna. Allt som kan sägas nu är att arton trettioendelar av mina sotlavkollekter är liten sotlav, det går inte att säga vilka som är det. Därför har jag bockat för "osäker artbestämning".</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
